--- a/public/templates/accounting-template.xlsx
+++ b/public/templates/accounting-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D6D0B9-2C0E-47C4-BA98-3830521FD62E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3258D8-016B-4C95-AC3F-94A606CD566B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="67">
   <si>
     <t>編號</t>
   </si>
@@ -262,6 +262,10 @@
   <si>
     <t>鐘點費
 單價</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>注：本學年度專任教師與導師基本鐘點差距為5節/週，一週5個工作日，代導一日公付1節鐘點。</t>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
 </sst>
@@ -470,7 +474,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -539,6 +543,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -551,7 +564,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -966,6 +979,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1002,8 +1018,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1262,22 +1278,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="107" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="140" t="s">
+      <c r="B1" s="141" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
       <c r="P1" s="116"/>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1578,22 +1594,22 @@
       <c r="O15" s="110"/>
     </row>
     <row r="16" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="141" t="s">
+      <c r="B16" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="142"/>
-      <c r="D16" s="142"/>
-      <c r="E16" s="142"/>
-      <c r="F16" s="142"/>
-      <c r="G16" s="142"/>
-      <c r="H16" s="142"/>
-      <c r="I16" s="142"/>
-      <c r="J16" s="142"/>
-      <c r="K16" s="142"/>
-      <c r="L16" s="142"/>
-      <c r="M16" s="142"/>
-      <c r="N16" s="142"/>
-      <c r="O16" s="143"/>
+      <c r="C16" s="143"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="143"/>
+      <c r="F16" s="143"/>
+      <c r="G16" s="143"/>
+      <c r="H16" s="143"/>
+      <c r="I16" s="143"/>
+      <c r="J16" s="143"/>
+      <c r="K16" s="143"/>
+      <c r="L16" s="143"/>
+      <c r="M16" s="143"/>
+      <c r="N16" s="143"/>
+      <c r="O16" s="144"/>
     </row>
     <row r="17" spans="2:16" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="134" t="s">
@@ -1721,21 +1737,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:77" s="83" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="144" t="s">
+      <c r="B1" s="145" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="145"/>
+      <c r="M1" s="145"/>
+      <c r="N1" s="145"/>
     </row>
     <row r="2" spans="1:77" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="84" t="s">
@@ -1986,19 +2002,19 @@
       <c r="BY10" s="75"/>
     </row>
     <row r="11" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="145"/>
-      <c r="C11" s="146"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="146"/>
-      <c r="F11" s="146"/>
-      <c r="G11" s="146"/>
-      <c r="H11" s="146"/>
-      <c r="I11" s="146"/>
-      <c r="J11" s="146"/>
-      <c r="K11" s="146"/>
-      <c r="L11" s="146"/>
-      <c r="M11" s="146"/>
-      <c r="N11" s="146"/>
+      <c r="B11" s="146"/>
+      <c r="C11" s="147"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="147"/>
+      <c r="H11" s="147"/>
+      <c r="I11" s="147"/>
+      <c r="J11" s="147"/>
+      <c r="K11" s="147"/>
+      <c r="L11" s="147"/>
+      <c r="M11" s="147"/>
+      <c r="N11" s="147"/>
       <c r="O11" s="75"/>
       <c r="P11" s="75"/>
       <c r="Q11" s="75"/>
@@ -2339,16 +2355,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="34" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="140" t="s">
+      <c r="B1" s="141" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="148"/>
+      <c r="G1" s="148"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="148"/>
       <c r="P1" s="35"/>
       <c r="Q1" s="36"/>
     </row>
@@ -2727,17 +2743,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="149" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
-      <c r="G1" s="149"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="149"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
     </row>
     <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -2993,7 +3009,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D6224E1-2B9C-43DA-8D8F-272D7D48239E}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" style="6" customWidth="1"/>
@@ -3009,17 +3025,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="139" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -3040,7 +3056,7 @@
       <c r="F2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="150" t="s">
+      <c r="G2" s="138" t="s">
         <v>65</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -3149,55 +3165,69 @@
       <c r="H11" s="14"/>
       <c r="I11" s="10"/>
     </row>
-    <row r="12" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+    <row r="12" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="151" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="151"/>
+      <c r="C12" s="151"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="151"/>
+      <c r="F12" s="151"/>
+      <c r="G12" s="151"/>
+      <c r="H12" s="151"/>
+      <c r="I12" s="151"/>
+    </row>
+    <row r="13" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B13" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15" t="s">
+      <c r="D13" s="15"/>
+      <c r="E13" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15" t="s">
+      <c r="F13" s="15"/>
+      <c r="G13" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="H12" s="16"/>
-      <c r="I12" s="17" t="s">
+      <c r="H13" s="16"/>
+      <c r="I13" s="17" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="15"/>
-    </row>
-    <row r="14" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15"/>
-      <c r="B14" s="15" t="s">
-        <v>45</v>
-      </c>
+      <c r="B14" s="15"/>
       <c r="D14" s="15"/>
-      <c r="E14" s="15" t="s">
-        <v>25</v>
-      </c>
+      <c r="E14" s="15"/>
       <c r="F14" s="15"/>
-      <c r="G14" s="15" t="s">
-        <v>46</v>
-      </c>
+      <c r="G14" s="15"/>
       <c r="H14" s="16"/>
       <c r="I14" s="15"/>
     </row>
+    <row r="15" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="16"/>
+      <c r="I15" s="15"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A12:I12"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3226,16 +3256,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="34" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="140" t="s">
+      <c r="B1" s="141" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="148"/>
+      <c r="G1" s="148"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="148"/>
       <c r="P1" s="35"/>
       <c r="Q1" s="36"/>
     </row>

--- a/public/templates/accounting-template.xlsx
+++ b/public/templates/accounting-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3258D8-016B-4C95-AC3F-94A606CD566B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA4CD46-2983-4AF7-9084-CCC35A31204B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="超鐘點" sheetId="5" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="66">
   <si>
     <t>編號</t>
   </si>
@@ -54,9 +54,6 @@
   <si>
     <t>請假
 扣超鐘節</t>
-  </si>
-  <si>
-    <t>鐘點費</t>
   </si>
   <si>
     <t>合計金額</t>
@@ -265,7 +262,11 @@
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
-    <t>注：本學年度專任教師與導師基本鐘點差距為5節/週，一週5個工作日，代導一日公付1節鐘點。</t>
+    <t>註：
+計算式：代導鐘點費 = (專任教師基本授課節數 - 導師基本授課節數) ÷ 每週授課天數 × 實際代理天數 × 鐘點費基準
+(1)115學年度專任教師與導師基本授課節數差距節數5節
+(2)一週以計算 5 日為基準（不含例假日）
+(3)鐘點費基準為代課鐘點費單價，115學年為國中每節455元</t>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
 </sst>
@@ -564,7 +565,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1019,7 +1020,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1268,7 +1272,7 @@
     <col min="7" max="7" width="6.5" style="113" customWidth="1"/>
     <col min="8" max="8" width="6.875" style="83" customWidth="1"/>
     <col min="9" max="9" width="9" style="73" customWidth="1"/>
-    <col min="10" max="10" width="8.125" style="83" customWidth="1"/>
+    <col min="10" max="10" width="8.75" style="83" customWidth="1"/>
     <col min="11" max="11" width="17.125" style="83" customWidth="1"/>
     <col min="12" max="13" width="0.25" style="91" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="12.75" style="91" hidden="1" customWidth="1"/>
@@ -1279,7 +1283,7 @@
   <sheetData>
     <row r="1" spans="1:16" s="107" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="141" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C1" s="141"/>
       <c r="D1" s="141"/>
@@ -1307,40 +1311,40 @@
         <v>2</v>
       </c>
       <c r="D2" s="117" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" s="118" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H2" s="39" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J2" s="39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K2" s="119" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="M2" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="41" t="s">
+      <c r="N2" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="120" t="s">
+      <c r="O2" s="119" t="s">
         <v>9</v>
-      </c>
-      <c r="O2" s="119" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -1578,7 +1582,7 @@
       </c>
       <c r="E15" s="133"/>
       <c r="F15" s="95" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15" s="95"/>
       <c r="H15" s="96"/>
@@ -1595,7 +1599,7 @@
     </row>
     <row r="16" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="142" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="143"/>
       <c r="D16" s="143"/>
@@ -1613,57 +1617,57 @@
     </row>
     <row r="17" spans="2:16" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="134" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="69"/>
       <c r="D17" s="70" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" s="75"/>
       <c r="F17" s="73"/>
       <c r="G17" s="70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H17" s="67"/>
       <c r="J17" s="73"/>
       <c r="K17" s="111" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L17" s="73"/>
       <c r="M17" s="67"/>
       <c r="N17" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="O17" s="112" t="s">
         <v>16</v>
-      </c>
-      <c r="O17" s="112" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="87.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="59"/>
       <c r="C18" s="69"/>
       <c r="D18" s="70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E18" s="75"/>
       <c r="F18" s="73"/>
       <c r="G18" s="70" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H18" s="67"/>
       <c r="J18" s="73"/>
       <c r="K18" s="111" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L18" s="73"/>
       <c r="M18" s="67"/>
       <c r="N18" s="67" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O18" s="77"/>
     </row>
     <row r="19" spans="2:16" ht="0.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K19" s="136" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="23.45" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1738,7 +1742,7 @@
   <sheetData>
     <row r="1" spans="1:77" s="83" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="145" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C1" s="145"/>
       <c r="D1" s="145"/>
@@ -1764,37 +1768,37 @@
         <v>2</v>
       </c>
       <c r="D2" s="87" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" s="88" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H2" s="87" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J2" s="87" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K2" s="89" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L2" s="90" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="89" t="s">
+      <c r="N2" s="86" t="s">
         <v>9</v>
-      </c>
-      <c r="N2" s="86" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:77" s="104" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2081,25 +2085,25 @@
     </row>
     <row r="12" spans="1:77" s="75" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="111" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="73"/>
       <c r="E12" s="73"/>
       <c r="F12" s="76" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G12" s="73"/>
       <c r="I12" s="74"/>
       <c r="J12" s="76" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K12" s="73"/>
       <c r="L12" s="67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M12" s="73"/>
       <c r="N12" s="111" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O12" s="91"/>
       <c r="P12" s="91"/>
@@ -2246,16 +2250,16 @@
       <c r="C14" s="73"/>
       <c r="E14" s="73"/>
       <c r="F14" s="76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G14" s="73"/>
       <c r="I14" s="74"/>
       <c r="J14" s="76" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K14" s="73"/>
       <c r="L14" s="67" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M14" s="73"/>
       <c r="N14" s="112"/>
@@ -2342,7 +2346,7 @@
     <col min="2" max="2" width="10.25" style="78" customWidth="1"/>
     <col min="3" max="3" width="9.625" style="79" customWidth="1"/>
     <col min="4" max="4" width="6.5" style="80" customWidth="1"/>
-    <col min="5" max="5" width="6.5" style="34" customWidth="1"/>
+    <col min="5" max="5" width="10.75" style="34" customWidth="1"/>
     <col min="6" max="6" width="13.375" style="34" customWidth="1"/>
     <col min="7" max="7" width="5.125" style="34" customWidth="1"/>
     <col min="8" max="8" width="19.125" style="81" customWidth="1"/>
@@ -2356,7 +2360,7 @@
   <sheetData>
     <row r="1" spans="1:17" s="34" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="141" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C1" s="148"/>
       <c r="D1" s="148"/>
@@ -2379,34 +2383,34 @@
         <v>2</v>
       </c>
       <c r="D2" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="40" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="120" t="s">
-        <v>27</v>
-      </c>
       <c r="H2" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="38" t="s">
         <v>9</v>
-      </c>
-      <c r="I2" s="38" t="s">
-        <v>10</v>
       </c>
       <c r="K2" s="42" t="s">
         <v>3</v>
       </c>
       <c r="L2" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="44" t="s">
-        <v>29</v>
-      </c>
       <c r="N2" s="43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2640,20 +2644,20 @@
     </row>
     <row r="15" spans="1:17" s="57" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="58" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="59"/>
       <c r="D15" s="60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E15" s="61"/>
       <c r="F15" s="62"/>
       <c r="G15" s="61" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H15" s="60"/>
       <c r="I15" s="63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="57" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2680,16 +2684,16 @@
       <c r="B18" s="65"/>
       <c r="C18" s="59"/>
       <c r="D18" s="60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E18" s="61"/>
       <c r="F18" s="62"/>
       <c r="G18" s="61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H18" s="60"/>
       <c r="I18" s="63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2736,7 +2740,7 @@
     <col min="4" max="4" width="20" style="29" customWidth="1"/>
     <col min="5" max="5" width="5.375" style="27" customWidth="1"/>
     <col min="6" max="6" width="10.25" style="15" customWidth="1"/>
-    <col min="7" max="7" width="11" style="15" customWidth="1"/>
+    <col min="7" max="7" width="13.25" style="15" customWidth="1"/>
     <col min="8" max="8" width="13.75" style="16" customWidth="1"/>
     <col min="9" max="9" width="36.25" style="27" customWidth="1"/>
     <col min="10" max="16384" width="9" style="19"/>
@@ -2744,7 +2748,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="149" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B1" s="150"/>
       <c r="C1" s="150"/>
@@ -2757,31 +2761,31 @@
     </row>
     <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="20" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="26.65" customHeight="1" x14ac:dyDescent="0.25">
@@ -2918,20 +2922,20 @@
     </row>
     <row r="15" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="27"/>
       <c r="D15" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G15" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="27" t="s">
         <v>39</v>
-      </c>
-      <c r="I15" s="27" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2949,14 +2953,14 @@
     </row>
     <row r="18" spans="1:9" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I18" s="15"/>
     </row>
@@ -3026,7 +3030,7 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="139" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B1" s="140"/>
       <c r="C1" s="140"/>
@@ -3039,31 +3043,31 @@
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G2" s="138" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3165,37 +3169,37 @@
       <c r="H11" s="14"/>
       <c r="I11" s="10"/>
     </row>
-    <row r="12" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="151" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="151"/>
-      <c r="C12" s="151"/>
-      <c r="D12" s="151"/>
-      <c r="E12" s="151"/>
-      <c r="F12" s="151"/>
-      <c r="G12" s="151"/>
-      <c r="H12" s="151"/>
-      <c r="I12" s="151"/>
+        <v>65</v>
+      </c>
+      <c r="B12" s="152"/>
+      <c r="C12" s="152"/>
+      <c r="D12" s="152"/>
+      <c r="E12" s="152"/>
+      <c r="F12" s="152"/>
+      <c r="G12" s="152"/>
+      <c r="H12" s="152"/>
+      <c r="I12" s="152"/>
     </row>
     <row r="13" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13" s="15"/>
       <c r="G13" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H13" s="16"/>
       <c r="I13" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -3211,15 +3215,15 @@
     <row r="15" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15"/>
       <c r="B15" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H15" s="16"/>
       <c r="I15" s="15"/>
@@ -3257,7 +3261,7 @@
   <sheetData>
     <row r="1" spans="1:17" s="34" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="141" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C1" s="148"/>
       <c r="D1" s="148"/>
@@ -3280,34 +3284,34 @@
         <v>2</v>
       </c>
       <c r="D2" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="40" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="120" t="s">
-        <v>27</v>
-      </c>
       <c r="H2" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="38" t="s">
         <v>9</v>
-      </c>
-      <c r="I2" s="38" t="s">
-        <v>10</v>
       </c>
       <c r="K2" s="42" t="s">
         <v>3</v>
       </c>
       <c r="L2" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="44" t="s">
-        <v>29</v>
-      </c>
       <c r="N2" s="43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3541,20 +3545,20 @@
     </row>
     <row r="15" spans="1:17" s="57" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="58" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="59"/>
       <c r="D15" s="60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E15" s="61"/>
       <c r="F15" s="62"/>
       <c r="G15" s="61" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H15" s="60"/>
       <c r="I15" s="63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="57" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3581,16 +3585,16 @@
       <c r="B18" s="65"/>
       <c r="C18" s="59"/>
       <c r="D18" s="60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E18" s="61"/>
       <c r="F18" s="62"/>
       <c r="G18" s="61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H18" s="60"/>
       <c r="I18" s="63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">

--- a/public/templates/accounting-template.xlsx
+++ b/public/templates/accounting-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA4CD46-2983-4AF7-9084-CCC35A31204B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B44E1A1-2B84-4857-801B-6E03D3588629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="超鐘點" sheetId="5" r:id="rId1"/>
@@ -475,7 +475,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -544,15 +544,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -983,46 +974,46 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1282,22 +1273,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="107" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="141" t="s">
+      <c r="B1" s="139" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
       <c r="P1" s="116"/>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1598,22 +1589,22 @@
       <c r="O15" s="110"/>
     </row>
     <row r="16" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="142" t="s">
+      <c r="B16" s="141" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="143"/>
-      <c r="D16" s="143"/>
-      <c r="E16" s="143"/>
-      <c r="F16" s="143"/>
-      <c r="G16" s="143"/>
-      <c r="H16" s="143"/>
-      <c r="I16" s="143"/>
-      <c r="J16" s="143"/>
-      <c r="K16" s="143"/>
-      <c r="L16" s="143"/>
-      <c r="M16" s="143"/>
-      <c r="N16" s="143"/>
-      <c r="O16" s="144"/>
+      <c r="C16" s="142"/>
+      <c r="D16" s="142"/>
+      <c r="E16" s="142"/>
+      <c r="F16" s="142"/>
+      <c r="G16" s="142"/>
+      <c r="H16" s="142"/>
+      <c r="I16" s="142"/>
+      <c r="J16" s="142"/>
+      <c r="K16" s="142"/>
+      <c r="L16" s="142"/>
+      <c r="M16" s="142"/>
+      <c r="N16" s="142"/>
+      <c r="O16" s="143"/>
     </row>
     <row r="17" spans="2:16" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="134" t="s">
@@ -1741,21 +1732,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:77" s="83" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="145" t="s">
+      <c r="B1" s="144" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
-      <c r="N1" s="145"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
+      <c r="M1" s="144"/>
+      <c r="N1" s="144"/>
     </row>
     <row r="2" spans="1:77" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="84" t="s">
@@ -2006,19 +1997,19 @@
       <c r="BY10" s="75"/>
     </row>
     <row r="11" spans="1:77" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="146"/>
-      <c r="C11" s="147"/>
-      <c r="D11" s="147"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="147"/>
-      <c r="G11" s="147"/>
-      <c r="H11" s="147"/>
-      <c r="I11" s="147"/>
-      <c r="J11" s="147"/>
-      <c r="K11" s="147"/>
-      <c r="L11" s="147"/>
-      <c r="M11" s="147"/>
-      <c r="N11" s="147"/>
+      <c r="B11" s="145"/>
+      <c r="C11" s="146"/>
+      <c r="D11" s="146"/>
+      <c r="E11" s="146"/>
+      <c r="F11" s="146"/>
+      <c r="G11" s="146"/>
+      <c r="H11" s="146"/>
+      <c r="I11" s="146"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="146"/>
+      <c r="L11" s="146"/>
+      <c r="M11" s="146"/>
+      <c r="N11" s="146"/>
       <c r="O11" s="75"/>
       <c r="P11" s="75"/>
       <c r="Q11" s="75"/>
@@ -2359,16 +2350,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="34" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="141" t="s">
+      <c r="B1" s="139" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
       <c r="P1" s="35"/>
       <c r="Q1" s="36"/>
     </row>
@@ -2747,17 +2738,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
+      <c r="B1" s="148"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="148"/>
+      <c r="G1" s="148"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="148"/>
     </row>
     <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -3029,17 +3020,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="149" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -3260,16 +3251,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="34" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="141" t="s">
+      <c r="B1" s="139" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
       <c r="P1" s="35"/>
       <c r="Q1" s="36"/>
     </row>
